--- a/Practice/04. Functions.xlsx
+++ b/Practice/04. Functions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="141">
   <si>
     <t>MAX</t>
   </si>
@@ -420,6 +421,33 @@
   </si>
   <si>
     <t>Avg Revenue of Widget C</t>
+  </si>
+  <si>
+    <t>Revinue of Widget A where units sold is 10</t>
+  </si>
+  <si>
+    <t>Revinue of Widget B where units sold is 5</t>
+  </si>
+  <si>
+    <t>Revinue of Widget C where units sold is 15</t>
+  </si>
+  <si>
+    <t>SUMIFS</t>
+  </si>
+  <si>
+    <t>Avg Revinue of Widget A where units sold is 10</t>
+  </si>
+  <si>
+    <t>AverageIFS</t>
+  </si>
+  <si>
+    <t>Avg Revinue of Widget B where units sold is 5</t>
+  </si>
+  <si>
+    <t>Avg Revinue of Widget C where units sold is 15</t>
+  </si>
+  <si>
+    <t>COUNTIFS</t>
   </si>
 </sst>
 </file>
@@ -446,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -820,11 +854,64 @@
     <xf numFmtId="2" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -897,6 +984,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C6500"/>
       </font>
       <fill>
@@ -907,21 +1004,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C6500"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3002,18 +3089,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D11">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
       <formula>180</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
       <formula>180</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>180</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>180</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3309,6 +3396,490 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B11">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Widget C">
+      <formula>NOT(ISERROR(SEARCH("Widget C",B2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Widget B">
+      <formula>NOT(ISERROR(SEARCH("Widget B",B2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Widget A">
+      <formula>NOT(ISERROR(SEARCH("Widget A",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="39.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="75">
+        <v>45536</v>
+      </c>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="76">
+        <v>200</v>
+      </c>
+      <c r="G2" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="75">
+        <v>45536</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="76">
+        <v>150</v>
+      </c>
+      <c r="G3" s="78">
+        <f>SUMIFS(E2:E21,B2:B21,"Widget A",D2:D21,10)</f>
+        <v>450</v>
+      </c>
+      <c r="H3" s="10">
+        <f>COUNTIFS(B2:B21,"Widget A",D2:D21,10)</f>
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="75">
+        <v>45537</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4" s="76">
+        <v>140</v>
+      </c>
+      <c r="G4" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="75">
+        <v>45537</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5" s="76">
+        <v>300</v>
+      </c>
+      <c r="G5" s="80">
+        <f>SUMIFS(E2:E21,B2:B21,"Widget B",D2:D21,5)</f>
+        <v>300</v>
+      </c>
+      <c r="H5" s="10">
+        <f>COUNTIFS(B2:B21,"Widget B",D2:D21,5)</f>
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="75">
+        <v>45538</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6" s="76">
+        <v>240</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="75">
+        <v>45538</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7" s="76">
+        <v>240</v>
+      </c>
+      <c r="G7" s="82">
+        <f>SUMIFS(E2:E21,B2:B21,"Widget C",D2:D21,15)</f>
+        <v>600</v>
+      </c>
+      <c r="H7" s="10">
+        <f>COUNTIFS(B2:B21,"Widget C",D2:D21,15)</f>
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <v>45539</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8" s="76">
+        <v>120</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="75">
+        <v>45539</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9" s="76">
+        <v>300</v>
+      </c>
+      <c r="G9" s="83" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="75">
+        <v>45540</v>
+      </c>
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10" s="76">
+        <v>160</v>
+      </c>
+      <c r="G10" s="78">
+        <f>AVERAGEIFS(E2:E21,B2:B21,"Widget A",D2:D21,10)</f>
+        <v>225</v>
+      </c>
+      <c r="H10" s="10">
+        <f>COUNTIFS(B2:B21,"Widget A",D2:D21,10)</f>
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="75">
+        <v>45540</v>
+      </c>
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="76">
+        <v>100</v>
+      </c>
+      <c r="G11" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>45536</v>
+      </c>
+      <c r="B12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" s="76">
+        <v>250</v>
+      </c>
+      <c r="G12" s="80">
+        <f>AVERAGEIFS(E2:E21,B2:B21,"Widget B",D2:D21,5)</f>
+        <v>150</v>
+      </c>
+      <c r="H12" s="10">
+        <f>COUNTIFS(B2:B21,"Widget B",D2:D21,5)</f>
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="75">
+        <v>45536</v>
+      </c>
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="76">
+        <v>150</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="75">
+        <v>45537</v>
+      </c>
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14" s="76">
+        <v>140</v>
+      </c>
+      <c r="G14" s="82">
+        <f>AVERAGEIFS(E2:E21,B2:B21,"Widget C",D2:D21,15)</f>
+        <v>300</v>
+      </c>
+      <c r="H14" s="10">
+        <f>COUNTIFS(B2:B21,"Widget C",D2:D21,15)</f>
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="75">
+        <v>45537</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15" s="76">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="75">
+        <v>45538</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" s="76">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="75">
+        <v>45538</v>
+      </c>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="E17" s="76">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="75">
+        <v>45539</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18" s="76">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="75">
+        <v>45539</v>
+      </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" s="76">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="75">
+        <v>45540</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20" s="76">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="75">
+        <v>45540</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" s="76">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Widget C">
       <formula>NOT(ISERROR(SEARCH("Widget C",B2)))</formula>
     </cfRule>

--- a/Practice/04. Functions.xlsx
+++ b/Practice/04. Functions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="151">
   <si>
     <t>MAX</t>
   </si>
@@ -448,6 +449,188 @@
   </si>
   <si>
     <t>COUNTIFS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YEAR()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Returns the year from a date.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONTH()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Returns the month from a date.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DAY(): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Returns the day of the month from a date.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NOW(): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Returnes the current date and time.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DAYS()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Returns the number of days between two dates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">WEEKDAY(): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Returns the day of the week as a number.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DATE(): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creates a date from year, month, and day values.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TODAY()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Returns the Current Date</t>
+    </r>
+  </si>
+  <si>
+    <t>OUTPUTS</t>
+  </si>
+  <si>
+    <t>FORMULAS</t>
   </si>
 </sst>
 </file>
@@ -542,7 +725,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -650,11 +833,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -877,11 +1140,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -969,36 +1256,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3892,4 +4149,107 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89">
+        <f ca="1">TODAY()</f>
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="87" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89">
+        <f>DATE(2000,2,13)</f>
+        <v>36569</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="87" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="88"/>
+      <c r="C4" s="90">
+        <f ca="1">WEEKDAY(C2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="88"/>
+      <c r="C5" s="90">
+        <f ca="1">_xlfn.DAYS(C2,C3)</f>
+        <v>9301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="87" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="92">
+        <f ca="1">NOW()</f>
+        <v>45870.693218171298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="88"/>
+      <c r="C7" s="90">
+        <f>DAY(C3)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="87" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="88"/>
+      <c r="C8" s="90">
+        <f ca="1">MONTH(C2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="94"/>
+      <c r="C9" s="95">
+        <f>YEAR(C3)</f>
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>